--- a/artfynd/S 1062-2026 artfynd.xlsx
+++ b/artfynd/S 1062-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575671</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575672</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575673</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111803636</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111803784</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575610</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575616</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575618</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1613,6 +1658,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575619</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1714,6 +1764,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575622</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1815,6 +1870,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575624</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1916,6 +1976,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575628</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2017,6 +2082,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575631</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2118,6 +2188,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575634</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2219,6 +2294,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575636</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2320,6 +2400,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575638</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2421,6 +2506,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575639</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2522,6 +2612,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575657</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2623,6 +2718,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575659</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2731,6 +2831,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111802870</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2839,6 +2944,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111802888</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2947,6 +3057,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111802970</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3055,6 +3170,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111803012</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3161,6 +3281,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113887756</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3262,6 +3387,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575658</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3370,6 +3500,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111803432</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3471,6 +3606,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575661</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3581,6 +3721,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575662</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3691,6 +3836,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575663</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3792,6 +3942,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575668</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3902,6 +4057,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575669</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4003,6 +4163,11 @@
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2019</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80575670</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4111,6 +4276,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111803757</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4219,8 +4389,49 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111802717</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>